--- a/out/해달게임_요리_재료_정리.xlsx
+++ b/out/해달게임_요리_재료_정리.xlsx
@@ -63,10 +63,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -434,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C57"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -649,12 +648,12 @@
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>gain_per</t>
+          <t>recipe</t>
         </is>
       </c>
       <c r="C16" s="1" t="inlineStr">
         <is>
-          <t>재료 얻는 확률</t>
+          <t>해당 요리에 필요한 재료의 rec_n 목록(오름차순, 공백 구분)</t>
         </is>
       </c>
     </row>
@@ -664,12 +663,12 @@
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>gain_loc</t>
+          <t>recipe_cnt</t>
         </is>
       </c>
       <c r="C17" s="1" t="inlineStr">
         <is>
-          <t>재료 얻는 위치(상점 제외)</t>
+          <t>recipe의 각 재료별 필요 수량(recipe와 동일 순서, 공백 구분)</t>
         </is>
       </c>
     </row>
@@ -855,7 +854,7 @@
       </c>
       <c r="C32" s="1" t="inlineStr">
         <is>
-          <t>주재료(해산물). 상점/엘프 상점에서 구매, 수량 소모</t>
+          <t>주재료(해산물 등). 상점/엘프 상점에서 구매, 수량 소모</t>
         </is>
       </c>
     </row>
@@ -889,334 +888,87 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>craft</t>
-        </is>
-      </c>
-      <c r="B35" s="1" t="n">
-        <v>304</v>
-      </c>
-      <c r="C35" s="1" t="inlineStr">
-        <is>
-          <t>레시피로 직접 제작하는 조미료</t>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>grade</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="inlineStr">
+        <is>
+          <t>definition</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>grade</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>star</t>
-        </is>
-      </c>
-      <c r="C37" s="1" t="inlineStr">
-        <is>
-          <t>definition</t>
+          <t>기본 제공 메뉴. 단일 기구 사용, 즉시 조리 (Phase 1~2)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>★1</t>
         </is>
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>기본</t>
-        </is>
-      </c>
-      <c r="C38" s="1" t="inlineStr">
-        <is>
-          <t>기본 제공 메뉴</t>
+          <t>밑간 또는 간단한 손질 (Phase 2~3)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>★2</t>
         </is>
       </c>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>★1</t>
-        </is>
-      </c>
-      <c r="C39" s="1" t="inlineStr">
-        <is>
-          <t>밑간 또는 간단한 손질</t>
+          <t>손질과 가열의 연계 (Phase 3~4)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>★3</t>
         </is>
       </c>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>★2</t>
-        </is>
-      </c>
-      <c r="C40" s="1" t="inlineStr">
-        <is>
-          <t>손질과 가열의 연계</t>
+          <t>중간 재료 제작 (Phase 4~5)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>★4</t>
         </is>
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>★3</t>
-        </is>
-      </c>
-      <c r="C41" s="1" t="inlineStr">
-        <is>
-          <t>중간 재료 제작</t>
+          <t>복수 조리 기구와 타이밍 관리 (Phase 5~6)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>★5</t>
         </is>
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>★4</t>
-        </is>
-      </c>
-      <c r="C42" s="1" t="inlineStr">
-        <is>
-          <t>복수 조리 기구와 타이밍 관리</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B43" s="1" t="inlineStr">
-        <is>
-          <t>★5</t>
-        </is>
-      </c>
-      <c r="C43" s="1" t="inlineStr">
-        <is>
-          <t>여러 재료의 동시 진행과 최종 조립</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>num</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>내용</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B46" s="1" t="inlineStr">
-        <is>
-          <t>출처</t>
-        </is>
-      </c>
-      <c r="C46" s="1" t="inlineStr">
-        <is>
-          <t>노션 「실제 인게임」(요리&amp;레시피 하위) 문서 기준으로 작성</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B47" s="1" t="inlineStr">
-        <is>
-          <t>잠정값</t>
-        </is>
-      </c>
-      <c r="C47" s="1" t="inlineStr">
-        <is>
-          <t>menu_t(요리시간)·price(가격)는 원문에 수치가 없어 등급별로 임의 배분한 잠정값. 노란색 헤더 표시. 밸런싱 시 확정 필요</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B48" s="1" t="inlineStr">
-        <is>
-          <t>잠정값 근거</t>
-        </is>
-      </c>
-      <c r="C48" s="1" t="inlineStr">
-        <is>
-          <t>menu_t는 등급별 권장 Phase 수(기본1~2 … ★5 6~7)에 비례 배분 / price는 등급별 등비 배분</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="B49" s="1" t="inlineStr">
-        <is>
-          <t>확인 필요</t>
-        </is>
-      </c>
-      <c r="C49" s="1" t="inlineStr">
-        <is>
-          <t>원문에 총 메뉴 18개로 기재되어 있으나 실제 표를 세면 22개(기본4+★1 3+★2 4+★3 4+★4 4+★5 3). 본 파일은 22개 기준</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="B50" s="1" t="inlineStr">
-        <is>
-          <t>확인 필요</t>
-        </is>
-      </c>
-      <c r="C50" s="1" t="inlineStr">
-        <is>
-          <t>recipe 컬럼에 재료 수량을 담는 필드가 없음. 원문에는 수량 존재(조개3, 새우2, 바지락3 등) → 수량 표기 방식 결정 필요</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="B51" s="1" t="inlineStr">
-        <is>
-          <t>확인 필요</t>
-        </is>
-      </c>
-      <c r="C51" s="1" t="inlineStr">
-        <is>
-          <t>「가리비 버터간장구이」는 메뉴명에 버터가 있으나 필요 재료에 버터가 없음(조미료 목록 전체에도 없음)</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="B52" s="1" t="inlineStr">
-        <is>
-          <t>확인 필요</t>
-        </is>
-      </c>
-      <c r="C52" s="1" t="inlineStr">
-        <is>
-          <t>미사용 재료 6종: 깨, 올리고당, 허브, 머스타드, 마요네즈, 참기름 (22개 메뉴 어디에도 쓰이지 않음)</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="B53" s="1" t="inlineStr">
-        <is>
-          <t>확인 필요</t>
-        </is>
-      </c>
-      <c r="C53" s="1" t="inlineStr">
-        <is>
-          <t>grade(F~A)와 star(★)는 회의 미확정 사항. 현재 기본=F … ★5=A 로 매핑</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="B54" s="1" t="inlineStr">
-        <is>
-          <t>확인 필요</t>
-        </is>
-      </c>
-      <c r="C54" s="1" t="inlineStr">
-        <is>
-          <t>type_n 102는 섬 탐험 삭제 확정에 따라 기존 learn(탐험/쿠킹마마) → research(연구실)로 재정의함</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="B55" s="1" t="inlineStr">
-        <is>
-          <t>확인 필요</t>
-        </is>
-      </c>
-      <c r="C55" s="1" t="inlineStr">
-        <is>
-          <t>class_n 205(복합 조리)는 「바다의 진미 플래터」 때문에 신규 추가</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="B56" s="1" t="inlineStr">
-        <is>
-          <t>컬럼 추가</t>
-        </is>
-      </c>
-      <c r="C56" s="1" t="inlineStr">
-        <is>
-          <t>ingredient 시트에 ing_type 컬럼 1개 추가(원본 대비). 재료 획득 경로 구분용</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="B57" s="1" t="inlineStr">
-        <is>
-          <t>gain_per/loc</t>
-        </is>
-      </c>
-      <c r="C57" s="1" t="inlineStr">
-        <is>
-          <t>섬 탐험 삭제로 재료 획득처가 상점뿐이므로 전 재료 null 유지</t>
+          <t>여러 재료의 동시 진행과 최종 조립 (Phase 6~7)</t>
         </is>
       </c>
     </row>
@@ -1231,756 +983,872 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>menu_n</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>m_name</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>type_n</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>class_n</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>menu_t</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>recipe</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>recipe_cnt</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>grade</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>가리비 구이</t>
         </is>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="C2" s="2" t="n">
         <v>101</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" s="2" t="n">
         <v>201</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>1001</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="n">
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>기본</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>새우 구이</t>
         </is>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C3" s="2" t="n">
         <v>101</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" s="2" t="n">
         <v>201</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>1002 1011</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="n">
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>1001 1012</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>1 1</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>기본</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>조개 찜</t>
         </is>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="C4" s="2" t="n">
         <v>101</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="2" t="n">
         <v>204</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>1003</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="n">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>기본</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>광어 회</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="C5" s="2" t="n">
         <v>101</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="2" t="n">
         <v>202</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>1004</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="n">
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>기본</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>문어 숙회</t>
         </is>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="C6" s="2" t="n">
         <v>102</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" s="2" t="n">
         <v>204</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>1005 1011</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="n">
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1006 1012</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1 1</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>★1</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="n">
         <v>80</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>새우 튀김</t>
         </is>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="C7" s="2" t="n">
         <v>102</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" s="2" t="n">
         <v>203</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>1002 1031</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="n">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1001 1011</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1 1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>★1</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="n">
         <v>80</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>고등어 구이</t>
         </is>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="C8" s="2" t="n">
         <v>102</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" s="2" t="n">
         <v>201</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>1006 1011</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="n">
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1007 1012</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1 1</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>★1</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="n">
         <v>80</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>오징어 숙회</t>
         </is>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="C9" s="2" t="n">
         <v>102</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D9" s="2" t="n">
         <v>204</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="E9" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>1007 1011</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="n">
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1003 1012</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1 1</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>★2</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="n">
         <v>130</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>바지락 술찜</t>
         </is>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="C10" s="2" t="n">
         <v>102</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="D10" s="2" t="n">
         <v>204</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="E10" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>1008 1022 1024</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="n">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1009 1021 1023</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3 1 1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>★2</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="n">
         <v>130</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>연어 간장구이</t>
         </is>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="C11" s="2" t="n">
         <v>102</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="D11" s="2" t="n">
         <v>201</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="E11" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>1009 1012 1021 1022</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="n">
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1008 1013 1020 1021</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1 1 1 1</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>★2</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="n">
         <v>130</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>가리비 버터간장구이</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="n">
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>가리비 간장구이</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
         <v>102</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="D12" s="2" t="n">
         <v>201</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="E12" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>1001 1012 1013 1021</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="n">
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1002 1013 1014 1020</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1 1 1 1</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>★2</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="n">
         <v>130</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>생선가스</t>
         </is>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="C13" s="2" t="n">
         <v>102</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="D13" s="2" t="n">
         <v>203</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="E13" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>1010 1011 1018 1027 1031</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="n">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1010 1011 1012 1017 1026</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1 1 1 1 1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>★3</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="n">
         <v>200</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>새우 완자탕</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="C14" s="2" t="n">
         <v>102</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="D14" s="2" t="n">
         <v>204</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="E14" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>1002 1011 1014 1017 1021</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="n">
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1001 1012 1015 1016 1020</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2 1 1 1 1</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>★3</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="n">
         <v>200</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>고등어 된장조림</t>
         </is>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="C15" s="2" t="n">
         <v>102</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="D15" s="2" t="n">
         <v>204</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="E15" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>1006 1012 1022 1025 1026</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="n">
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>1007 1013 1021 1024 1025</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>1 1 1 1 1</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>★3</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="n">
         <v>200</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>문어 초무침</t>
         </is>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="C16" s="2" t="n">
         <v>102</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="D16" s="2" t="n">
         <v>202</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="E16" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>1005 1011 1012 1019 1030</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="n">
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1006 1012 1013 1018 1028</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1 1 1 1 1</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>★3</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="n">
         <v>200</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>해물 크림스튜</t>
         </is>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="C17" s="2" t="n">
         <v>102</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="D17" s="2" t="n">
         <v>204</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="E17" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>1001 1002 1007 1011 1013 1017 1018</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="n">
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1001 1002 1003 1012 1014 1016 1017</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1 1 1 1 1 1 1</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>★4</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="n">
         <v>300</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>연어 스테이크 레몬소스</t>
         </is>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="C18" s="2" t="n">
         <v>102</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="D18" s="2" t="n">
         <v>201</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="E18" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>1009 1011 1013 1017 1023 1028</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="n">
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>1008 1012 1014 1016 1022 1027</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1 1 1 1 1 1</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>★4</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="n">
         <v>300</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>해물 튀김 모둠</t>
         </is>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="C19" s="2" t="n">
         <v>102</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="D19" s="2" t="n">
         <v>203</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="E19" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>1002 1003 1007 1011 1018 1027 1031</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="n">
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>1001 1003 1004 1011 1012 1017 1026</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1 1 2 1 1 1 1</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>★4</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="n">
         <v>300</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>광어 간장찜</t>
         </is>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="C20" s="2" t="n">
         <v>102</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="D20" s="2" t="n">
         <v>204</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="E20" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>1004 1012 1021 1022 1024 1026</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="n">
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1005 1013 1020 1021 1023 1025</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1 1 1 1 1 1</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>★4</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="n">
         <v>300</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>해산물 전골</t>
         </is>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="C21" s="2" t="n">
         <v>102</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="D21" s="2" t="n">
         <v>204</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="E21" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>1001 1002 1003 1005 1021 1024 1025 1026</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="n">
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>1001 1002 1004 1006 1020 1023 1024 1025</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>1 1 3 1 1 1 1 1</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>★5</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="n">
         <v>450</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>해물 된장구이 모둠</t>
         </is>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="C22" s="2" t="n">
         <v>102</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="D22" s="2" t="n">
         <v>201</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="E22" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>1001 1002 1009 1022 1025 1026 1028</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="n">
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>1001 1002 1008 1021 1024 1025 1027</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1 1 1 1 1 1 1</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>★5</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="n">
         <v>450</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>바다의 진미 플래터</t>
         </is>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="C23" s="2" t="n">
         <v>102</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="D23" s="2" t="n">
         <v>205</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="E23" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>1001 1002 1004 1005 1011 1020 1021 1023</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="n">
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>1001 1002 1005 1006 1012 1019 1020 1022</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>1 1 1 1 1 1 1 1</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>★5</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="n">
         <v>450</v>
       </c>
     </row>
@@ -1995,926 +1863,480 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>ing_n</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>ing_name</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>rec_n</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>gain_per</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>gain_loc</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>ing_type</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>새우</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>1001</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>가리비</t>
         </is>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>1001</v>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="n">
+      <c r="C3" s="2" t="n">
+        <v>1002</v>
+      </c>
+      <c r="D3" s="2" t="n">
         <v>301</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>새우</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>1002</v>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="n">
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>오징어</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>1003</v>
+      </c>
+      <c r="D4" s="2" t="n">
         <v>301</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>조개</t>
         </is>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>1003</v>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="n">
+      <c r="C5" s="2" t="n">
+        <v>1004</v>
+      </c>
+      <c r="D5" s="2" t="n">
         <v>301</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>광어</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n">
-        <v>1004</v>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="n">
+      <c r="C6" s="2" t="n">
+        <v>1005</v>
+      </c>
+      <c r="D6" s="2" t="n">
         <v>301</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>문어</t>
         </is>
       </c>
-      <c r="C6" s="3" t="n">
-        <v>1005</v>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="n">
+      <c r="C7" s="2" t="n">
+        <v>1006</v>
+      </c>
+      <c r="D7" s="2" t="n">
         <v>301</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>고등어</t>
         </is>
       </c>
-      <c r="C7" s="3" t="n">
-        <v>1006</v>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="n">
+      <c r="C8" s="2" t="n">
+        <v>1007</v>
+      </c>
+      <c r="D8" s="2" t="n">
         <v>301</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>오징어</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>1007</v>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="n">
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>연어</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>1008</v>
+      </c>
+      <c r="D9" s="2" t="n">
         <v>301</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>바지락</t>
         </is>
       </c>
-      <c r="C9" s="3" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="n">
+      <c r="C10" s="2" t="n">
+        <v>1009</v>
+      </c>
+      <c r="D10" s="2" t="n">
         <v>301</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>연어</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="n">
-        <v>1009</v>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="n">
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>흰살생선</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>1010</v>
+      </c>
+      <c r="D11" s="2" t="n">
         <v>301</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>흰살생선</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="n">
-        <v>1010</v>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="n">
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>튀김가루</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>1011</v>
+      </c>
+      <c r="D12" s="2" t="n">
         <v>301</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>소금</t>
         </is>
       </c>
-      <c r="C12" s="3" t="n">
-        <v>1011</v>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="n">
+      <c r="C13" s="2" t="n">
+        <v>1012</v>
+      </c>
+      <c r="D13" s="2" t="n">
         <v>302</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>설탕</t>
         </is>
       </c>
-      <c r="C13" s="3" t="n">
-        <v>1012</v>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="n">
+      <c r="C14" s="2" t="n">
+        <v>1013</v>
+      </c>
+      <c r="D14" s="2" t="n">
         <v>302</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>식용유</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n">
-        <v>1013</v>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="n">
+      <c r="C15" s="2" t="n">
+        <v>1014</v>
+      </c>
+      <c r="D15" s="2" t="n">
         <v>302</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>전분</t>
         </is>
       </c>
-      <c r="C15" s="3" t="n">
-        <v>1014</v>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="n">
+      <c r="C16" s="2" t="n">
+        <v>1015</v>
+      </c>
+      <c r="D16" s="2" t="n">
         <v>302</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>깨</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>1015</v>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="n">
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>후추</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>1016</v>
+      </c>
+      <c r="D17" s="2" t="n">
         <v>302</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>올리고당</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="n">
-        <v>1016</v>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="n">
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>밀가루</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>1017</v>
+      </c>
+      <c r="D18" s="2" t="n">
         <v>302</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>후추</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="n">
-        <v>1017</v>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>302</v>
-      </c>
-    </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>밀가루</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="n">
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>식초</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n">
         <v>1018</v>
       </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>302</v>
+      <c r="D19" s="2" t="n">
+        <v>303</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>식초</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="n">
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>와사비</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="n">
         <v>1019</v>
       </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="n">
+      <c r="D20" s="2" t="n">
         <v>303</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>와사비</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="n">
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>간장</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
         <v>1020</v>
       </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="n">
+      <c r="D21" s="2" t="n">
         <v>303</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>간장</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="n">
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>미림</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n">
         <v>1021</v>
       </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="n">
+      <c r="D22" s="2" t="n">
         <v>303</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>미림</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="n">
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>레몬</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="n">
         <v>1022</v>
       </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="n">
+      <c r="D23" s="2" t="n">
         <v>303</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>레몬</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="n">
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>마늘</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="n">
         <v>1023</v>
       </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="n">
+      <c r="D24" s="2" t="n">
         <v>303</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>마늘</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="n">
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>된장</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
         <v>1024</v>
       </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="n">
+      <c r="D25" s="2" t="n">
         <v>303</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>된장</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="n">
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>생강</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
         <v>1025</v>
       </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="n">
+      <c r="D26" s="2" t="n">
         <v>303</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>생강</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="n">
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>계란</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
         <v>1026</v>
       </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="n">
+      <c r="D27" s="2" t="n">
         <v>303</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>계란</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="n">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>꿀</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
         <v>1027</v>
       </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="n">
+      <c r="D28" s="2" t="n">
         <v>303</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>꿀</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="n">
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>겨자</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
         <v>1028</v>
       </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="n">
+      <c r="D29" s="2" t="n">
         <v>303</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>허브</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="n">
-        <v>1029</v>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="n">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>겨자</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="n">
-        <v>1030</v>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="n">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>튀김가루</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="n">
-        <v>1031</v>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>머스타드</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="n">
-        <v>1032</v>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>마요네즈</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="n">
-        <v>1033</v>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="n">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>참기름</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="n">
-        <v>1034</v>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>304</v>
       </c>
     </row>
   </sheetData>
